--- a/flows/vol-17/タスク一覧.xlsx
+++ b/flows/vol-17/タスク一覧.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
